--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/MARYLAND_2012.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/MARYLAND_2012.xlsx
@@ -1932,7 +1932,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C88">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C392">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C410">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C412">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C684">
